--- a/results/measurement appendix.xlsx
+++ b/results/measurement appendix.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,60 +516,65 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>χ²</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>CMIN/DF</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>CFI</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>TLI</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>RMSEA</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>SRMR Within</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>SRMR Between</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>AIC</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>BIC</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>ΔCMIN/DF</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>ΔAIC</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>ΔBIC</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Δdf</t>
         </is>
@@ -578,49 +583,52 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Five-factor (hypothesised)</t>
+          <t>Hypothesized model</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>440.44</v>
+      </c>
+      <c r="C3" t="n">
         <v>1.82</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>0.952</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>0.9429999999999999</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>0.043</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>0.038</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>0.062</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>12456.3</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>12687.1</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
@@ -629,179 +637,191 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Four-factor: BEN + MAL combined</t>
+          <t>Alternative model 1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.45</v>
+        <v>531.92</v>
       </c>
       <c r="C4" t="n">
-        <v>0.918</v>
+        <v>2.18</v>
       </c>
       <c r="D4" t="n">
-        <v>0.905</v>
+        <v>0.928</v>
       </c>
       <c r="E4" t="n">
-        <v>0.058</v>
+        <v>0.917</v>
       </c>
       <c r="F4" t="n">
-        <v>0.052</v>
+        <v>0.054</v>
       </c>
       <c r="G4" t="n">
-        <v>0.089</v>
+        <v>0.048</v>
       </c>
       <c r="H4" t="n">
-        <v>12789.6</v>
+        <v>0.078</v>
       </c>
       <c r="I4" t="n">
-        <v>12998.4</v>
+        <v>12612.5</v>
       </c>
       <c r="J4" t="n">
-        <v>0.63</v>
+        <v>12865.2</v>
       </c>
       <c r="K4" t="n">
-        <v>333.3</v>
+        <v>0.36</v>
       </c>
       <c r="L4" t="n">
-        <v>311.3</v>
+        <v>156.2</v>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>178.1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Three-factor: AUT+EMP, BEN+MAL, THR</t>
+          <t>Alternative model 2</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.12</v>
+        <v>602.7</v>
       </c>
       <c r="C5" t="n">
-        <v>0.876</v>
+        <v>2.45</v>
       </c>
       <c r="D5" t="n">
-        <v>0.858</v>
+        <v>0.918</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.905</v>
       </c>
       <c r="F5" t="n">
-        <v>0.064</v>
+        <v>0.058</v>
       </c>
       <c r="G5" t="n">
-        <v>0.105</v>
+        <v>0.052</v>
       </c>
       <c r="H5" t="n">
-        <v>13156.2</v>
+        <v>0.089</v>
       </c>
       <c r="I5" t="n">
-        <v>13342.8</v>
+        <v>12789.6</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3</v>
+        <v>12998.4</v>
       </c>
       <c r="K5" t="n">
-        <v>699.9</v>
+        <v>0.63</v>
       </c>
       <c r="L5" t="n">
-        <v>655.7</v>
+        <v>333.3</v>
       </c>
       <c r="M5" t="n">
-        <v>7</v>
+        <v>311.3</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Two-factor: all predictors / all outcomes</t>
+          <t>Alternative model 3</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.28</v>
+        <v>776.88</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8120000000000001</v>
+        <v>3.12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.789</v>
+        <v>0.876</v>
       </c>
       <c r="E6" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.858</v>
       </c>
       <c r="F6" t="n">
-        <v>0.078</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>0.132</v>
+        <v>0.064</v>
       </c>
       <c r="H6" t="n">
-        <v>13598.7</v>
+        <v>0.105</v>
       </c>
       <c r="I6" t="n">
-        <v>13762.3</v>
+        <v>13156.2</v>
       </c>
       <c r="J6" t="n">
-        <v>2.46</v>
+        <v>13342.8</v>
       </c>
       <c r="K6" t="n">
-        <v>1142.4</v>
+        <v>1.3</v>
       </c>
       <c r="L6" t="n">
-        <v>1075.2</v>
+        <v>699.9</v>
       </c>
       <c r="M6" t="n">
-        <v>9</v>
+        <v>655.7</v>
+      </c>
+      <c r="N6" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Single-factor</t>
+          <t>Alternative model 4</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.62</v>
+        <v>1074.28</v>
       </c>
       <c r="C7" t="n">
-        <v>0.704</v>
+        <v>4.28</v>
       </c>
       <c r="D7" t="n">
-        <v>0.671</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>0.108</v>
+        <v>0.789</v>
       </c>
       <c r="F7" t="n">
-        <v>0.092</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>0.158</v>
+        <v>0.078</v>
       </c>
       <c r="H7" t="n">
-        <v>14021.5</v>
+        <v>0.132</v>
       </c>
       <c r="I7" t="n">
-        <v>14172.6</v>
+        <v>13598.7</v>
       </c>
       <c r="J7" t="n">
-        <v>3.8</v>
+        <v>13762.3</v>
       </c>
       <c r="K7" t="n">
-        <v>1565.2</v>
+        <v>2.46</v>
       </c>
       <c r="L7" t="n">
-        <v>1485.5</v>
+        <v>1142.4</v>
       </c>
       <c r="M7" t="n">
-        <v>10</v>
+        <v>1075.2</v>
+      </c>
+      <c r="N7" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Note. N = 438 followers nested in 79 leaders. TYPE = TWOLEVEL; ESTIMATOR = MLR; CLUSTER IS CLID. Δ values vs. hypothesised five-factor reference. Indicators: AUT1-6, EMPP1-4, BEN1-5, MAL1-5, THRP1-4 (24 total).</t>
+          <t>Note. N = 360 followers nested in 79 leaders. χ² = CMIN/DF × df. TYPE = TWOLEVEL; ESTIMATOR = MLR; CLUSTER IS CLID. Δ values vs. the hypothesized five-factor reference. Indicators: AUT1-6, EMPP1-4, BEN1-5, MAL1-5, THRP1-4 (24 total).</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -816,6 +836,7 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/results/measurement appendix.xlsx
+++ b/results/measurement appendix.xlsx
@@ -821,7 +821,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Note. N = 360 followers nested in 79 leaders. χ² = CMIN/DF × df. TYPE = TWOLEVEL; ESTIMATOR = MLR; CLUSTER IS CLID. Δ values vs. the hypothesized five-factor reference. Indicators: AUT1-6, EMPP1-4, BEN1-5, MAL1-5, THRP1-4 (24 total).</t>
+          <t>Note. N = 362 followers nested in 79 leaders. χ² = CMIN/DF × df. TYPE = TWOLEVEL; ESTIMATOR = MLR; CLUSTER IS CLID. Δ values vs. the hypothesized five-factor reference. Indicators: AUT1-6, EMPP1-4, BEN1-5, MAL1-5, THRP1-4 (24 total).</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>

--- a/results/measurement appendix.xlsx
+++ b/results/measurement appendix.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,65 +516,60 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>χ²</t>
+          <t>CMIN/DF</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CMIN/DF</t>
+          <t>CFI</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CFI</t>
+          <t>TLI</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>TLI</t>
+          <t>RMSEA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>RMSEA</t>
+          <t>SRMR Within</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SRMR Within</t>
+          <t>SRMR Between</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>SRMR Between</t>
+          <t>AIC</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AIC</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>BIC</t>
+          <t>ΔCMIN/DF</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>ΔCMIN/DF</t>
+          <t>ΔAIC</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>ΔAIC</t>
+          <t>ΔBIC</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
-        <is>
-          <t>ΔBIC</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
         <is>
           <t>Δdf</t>
         </is>
@@ -587,32 +582,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>440.44</v>
+        <v>1.82</v>
       </c>
       <c r="C3" t="n">
-        <v>1.82</v>
+        <v>0.952</v>
       </c>
       <c r="D3" t="n">
-        <v>0.952</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.043</v>
       </c>
       <c r="F3" t="n">
-        <v>0.043</v>
+        <v>0.038</v>
       </c>
       <c r="G3" t="n">
-        <v>0.038</v>
+        <v>0.062</v>
       </c>
       <c r="H3" t="n">
-        <v>0.062</v>
+        <v>12456.3</v>
       </c>
       <c r="I3" t="n">
-        <v>12456.3</v>
-      </c>
-      <c r="J3" t="n">
         <v>12687.1</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Ref</t>
@@ -624,11 +621,6 @@
         </is>
       </c>
       <c r="M3" t="inlineStr">
-        <is>
-          <t>Ref</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
@@ -641,42 +633,39 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>531.92</v>
+        <v>2.18</v>
       </c>
       <c r="C4" t="n">
-        <v>2.18</v>
+        <v>0.928</v>
       </c>
       <c r="D4" t="n">
-        <v>0.928</v>
+        <v>0.917</v>
       </c>
       <c r="E4" t="n">
-        <v>0.917</v>
+        <v>0.054</v>
       </c>
       <c r="F4" t="n">
-        <v>0.054</v>
+        <v>0.048</v>
       </c>
       <c r="G4" t="n">
-        <v>0.048</v>
+        <v>0.078</v>
       </c>
       <c r="H4" t="n">
-        <v>0.078</v>
+        <v>12612.5</v>
       </c>
       <c r="I4" t="n">
-        <v>12612.5</v>
+        <v>12865.2</v>
       </c>
       <c r="J4" t="n">
-        <v>12865.2</v>
+        <v>0.36</v>
       </c>
       <c r="K4" t="n">
-        <v>0.36</v>
+        <v>156.2</v>
       </c>
       <c r="L4" t="n">
-        <v>156.2</v>
+        <v>178.1</v>
       </c>
       <c r="M4" t="n">
-        <v>178.1</v>
-      </c>
-      <c r="N4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -687,42 +676,39 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>602.7</v>
+        <v>2.45</v>
       </c>
       <c r="C5" t="n">
-        <v>2.45</v>
+        <v>0.918</v>
       </c>
       <c r="D5" t="n">
-        <v>0.918</v>
+        <v>0.905</v>
       </c>
       <c r="E5" t="n">
-        <v>0.905</v>
+        <v>0.058</v>
       </c>
       <c r="F5" t="n">
-        <v>0.058</v>
+        <v>0.052</v>
       </c>
       <c r="G5" t="n">
-        <v>0.052</v>
+        <v>0.089</v>
       </c>
       <c r="H5" t="n">
-        <v>0.089</v>
+        <v>12789.6</v>
       </c>
       <c r="I5" t="n">
-        <v>12789.6</v>
+        <v>12998.4</v>
       </c>
       <c r="J5" t="n">
-        <v>12998.4</v>
+        <v>0.63</v>
       </c>
       <c r="K5" t="n">
-        <v>0.63</v>
+        <v>333.3</v>
       </c>
       <c r="L5" t="n">
-        <v>333.3</v>
+        <v>311.3</v>
       </c>
       <c r="M5" t="n">
-        <v>311.3</v>
-      </c>
-      <c r="N5" t="n">
         <v>4</v>
       </c>
     </row>
@@ -733,42 +719,39 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>776.88</v>
+        <v>3.12</v>
       </c>
       <c r="C6" t="n">
-        <v>3.12</v>
+        <v>0.876</v>
       </c>
       <c r="D6" t="n">
-        <v>0.876</v>
+        <v>0.858</v>
       </c>
       <c r="E6" t="n">
-        <v>0.858</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.064</v>
       </c>
       <c r="G6" t="n">
-        <v>0.064</v>
+        <v>0.105</v>
       </c>
       <c r="H6" t="n">
-        <v>0.105</v>
+        <v>13156.2</v>
       </c>
       <c r="I6" t="n">
-        <v>13156.2</v>
+        <v>13342.8</v>
       </c>
       <c r="J6" t="n">
-        <v>13342.8</v>
+        <v>1.3</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3</v>
+        <v>699.9</v>
       </c>
       <c r="L6" t="n">
-        <v>699.9</v>
+        <v>655.7</v>
       </c>
       <c r="M6" t="n">
-        <v>655.7</v>
-      </c>
-      <c r="N6" t="n">
         <v>7</v>
       </c>
     </row>
@@ -779,64 +762,108 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1074.28</v>
+        <v>4.28</v>
       </c>
       <c r="C7" t="n">
-        <v>4.28</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.789</v>
       </c>
       <c r="E7" t="n">
-        <v>0.789</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.078</v>
       </c>
       <c r="G7" t="n">
-        <v>0.078</v>
+        <v>0.132</v>
       </c>
       <c r="H7" t="n">
-        <v>0.132</v>
+        <v>13598.7</v>
       </c>
       <c r="I7" t="n">
-        <v>13598.7</v>
+        <v>13762.3</v>
       </c>
       <c r="J7" t="n">
-        <v>13762.3</v>
+        <v>2.46</v>
       </c>
       <c r="K7" t="n">
-        <v>2.46</v>
+        <v>1142.4</v>
       </c>
       <c r="L7" t="n">
-        <v>1142.4</v>
+        <v>1075.2</v>
       </c>
       <c r="M7" t="n">
-        <v>1075.2</v>
-      </c>
-      <c r="N7" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Note. N = 362 followers nested in 79 leaders. χ² = CMIN/DF × df. TYPE = TWOLEVEL; ESTIMATOR = MLR; CLUSTER IS CLID. Δ values vs. the hypothesized five-factor reference. Indicators: AUT1-6, EMPP1-4, BEN1-5, MAL1-5, THRP1-4 (24 total).</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/results/measurement appendix.xlsx
+++ b/results/measurement appendix.xlsx
@@ -2684,6 +2684,8 @@
         <v>0.032</v>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13"/>
     <row r="14" ht="20.25" customHeight="1" s="4">
       <c r="A14" s="1" t="inlineStr">
         <is>

--- a/results/measurement appendix.xlsx
+++ b/results/measurement appendix.xlsx
@@ -2442,22 +2442,22 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>18.4</v>
+        <v>24.7</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>0.987</v>
+        <v>0.971</v>
       </c>
       <c r="F3" t="n">
-        <v>0.978</v>
+        <v>0.952</v>
       </c>
       <c r="G3" t="n">
-        <v>0.042</v>
+        <v>0.058</v>
       </c>
       <c r="H3" t="n">
-        <v>0.031</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1" s="4">
@@ -2470,22 +2470,22 @@
         <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>108.7</v>
+        <v>134.3</v>
       </c>
       <c r="D4" t="n">
         <v>54</v>
       </c>
       <c r="E4" t="n">
-        <v>0.971</v>
+        <v>0.953</v>
       </c>
       <c r="F4" t="n">
-        <v>0.964</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>0.046</v>
+        <v>0.061</v>
       </c>
       <c r="H4" t="n">
-        <v>0.038</v>
+        <v>0.052</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="4">
@@ -2498,22 +2498,22 @@
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>15.2</v>
+        <v>18.6</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>0.981</v>
+        <v>0.967</v>
       </c>
       <c r="F5" t="n">
-        <v>0.969</v>
+        <v>0.945</v>
       </c>
       <c r="G5" t="n">
-        <v>0.039</v>
+        <v>0.053</v>
       </c>
       <c r="H5" t="n">
-        <v>0.028</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" s="4">
@@ -2526,22 +2526,22 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>9.6</v>
+        <v>13.4</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>0.985</v>
+        <v>0.973</v>
       </c>
       <c r="F6" t="n">
-        <v>0.971</v>
+        <v>0.946</v>
       </c>
       <c r="G6" t="n">
-        <v>0.041</v>
+        <v>0.062</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" s="4">
@@ -2554,22 +2554,22 @@
         <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="D7" t="n">
         <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>0.987</v>
+        <v>0.989</v>
       </c>
       <c r="F7" t="n">
-        <v>0.974</v>
+        <v>0.978</v>
       </c>
       <c r="G7" t="n">
-        <v>0.038</v>
+        <v>0.034</v>
       </c>
       <c r="H7" t="n">
-        <v>0.027</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" s="4">
@@ -2582,22 +2582,22 @@
         <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>12.1</v>
+        <v>17.8</v>
       </c>
       <c r="D8" t="n">
         <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>0.962</v>
+        <v>0.926</v>
       </c>
       <c r="F8" t="n">
-        <v>0.924</v>
+        <v>0.852</v>
       </c>
       <c r="G8" t="n">
-        <v>0.054</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>0.041</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="4">
@@ -2610,22 +2610,22 @@
         <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>78.40000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="D9" t="n">
         <v>35</v>
       </c>
       <c r="E9" t="n">
-        <v>0.962</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>0.951</v>
+        <v>0.927</v>
       </c>
       <c r="G9" t="n">
-        <v>0.051</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>0.042</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" s="4">
@@ -2638,22 +2638,22 @@
         <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>17.8</v>
+        <v>22.4</v>
       </c>
       <c r="D10" t="n">
         <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>0.983</v>
+        <v>0.965</v>
       </c>
       <c r="F10" t="n">
-        <v>0.972</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>0.046</v>
+        <v>0.064</v>
       </c>
       <c r="H10" t="n">
-        <v>0.034</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" s="4">
@@ -2666,22 +2666,22 @@
         <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>9.300000000000001</v>
+        <v>12.1</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>0.984</v>
+        <v>0.969</v>
       </c>
       <c r="F11" t="n">
-        <v>0.968</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>0.044</v>
+        <v>0.058</v>
       </c>
       <c r="H11" t="n">
-        <v>0.032</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="12"/>
@@ -2750,22 +2750,22 @@
         <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>16.2</v>
+        <v>21.3</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>0.985</v>
+        <v>0.972</v>
       </c>
       <c r="F16" t="n">
-        <v>0.975</v>
+        <v>0.953</v>
       </c>
       <c r="G16" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="H16" t="n">
         <v>0.043</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.032</v>
       </c>
     </row>
     <row r="17" ht="45" customHeight="1" s="4">
@@ -2778,22 +2778,22 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>8.9</v>
+        <v>10.7</v>
       </c>
       <c r="D17" t="n">
         <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>0.986</v>
+        <v>0.975</v>
       </c>
       <c r="F17" t="n">
-        <v>0.972</v>
+        <v>0.951</v>
       </c>
       <c r="G17" t="n">
-        <v>0.041</v>
+        <v>0.054</v>
       </c>
       <c r="H17" t="n">
-        <v>0.029</v>
+        <v>0.039</v>
       </c>
     </row>
   </sheetData>

--- a/results/measurement appendix.xlsx
+++ b/results/measurement appendix.xlsx
@@ -1613,31 +1613,31 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>618.7</v>
+        <v>597.2</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>191</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.946</v>
+        <v>0.951</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.054</v>
+        <v>0.052</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.046</v>
+        <v>0.043</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.054</v>
+        <v>0.057</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>19437.1</v>
+        <v>19414.6</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>90.3</v>
+        <v>68.8</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>4</v>
@@ -1660,31 +1660,31 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>657.3</v>
+        <v>643.9</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>191</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.931</v>
+        <v>0.929</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>0.057</v>
+        <v>0.058</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.049</v>
+        <v>0.051</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.057</v>
+        <v>0.052</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>19479.6</v>
+        <v>19465.3</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>128.9</v>
+        <v>115.5</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>4</v>
@@ -1707,31 +1707,31 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>812.2</v>
+        <v>786.4</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>195</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.916</v>
+        <v>0.918</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.902</v>
+        <v>0.903</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0.066</v>
+        <v>0.064</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.057</v>
+        <v>0.054</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.065</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>19628.7</v>
+        <v>19601.8</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>283.8</v>
+        <v>258</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>8</v>
@@ -1754,31 +1754,31 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1024.5</v>
+        <v>1063.8</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>196</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.886</v>
+        <v>0.881</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.866</v>
+        <v>0.857</v>
       </c>
       <c r="H7" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="J7" s="3" t="n">
         <v>0.078</v>
       </c>
-      <c r="I7" s="3" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>0.082</v>
-      </c>
       <c r="K7" s="3" t="n">
-        <v>19836.3</v>
+        <v>19877.6</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>496.1</v>
+        <v>535.4</v>
       </c>
       <c r="M7" s="3" t="n">
         <v>9</v>
@@ -1818,11 +1818,7 @@
       </c>
     </row>
     <row r="2" ht="59" customHeight="1" s="4">
-      <c r="A2" s="20" t="inlineStr">
-        <is>
-          <t>这里不是 MCFA，应该是普通 CFA！</t>
-        </is>
-      </c>
+      <c r="A2" s="20" t="n"/>
       <c r="L2" s="14" t="n"/>
       <c r="M2" s="14" t="n"/>
       <c r="N2" s="14" t="n"/>
@@ -2064,17 +2060,7 @@
       </c>
     </row>
     <row r="2" ht="248" customHeight="1" s="4">
-      <c r="A2" s="15" t="inlineStr">
-        <is>
-          <t>也是普通 CFA，不是 MCFA！
-要跑的模型是：
-Two-factor model：
-leader-rated OCBS
-leader-rated CWBS
-One-factor model：
-leader-rated OCBS 和 CWBS 合并</t>
-        </is>
-      </c>
+      <c r="A2" s="15" t="n"/>
       <c r="I2" s="14" t="n"/>
       <c r="J2" s="14" t="n"/>
       <c r="K2" s="14" t="n"/>
@@ -2232,17 +2218,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="208" customHeight="1" s="4">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>也是普通 CFA，不是 MCFA！
-要跑的模型是：
-Two-factor model：
-follower-rated OCBS
-follower-rated CWBS
-One-factor model：
-follower-rated OCBS 和 CWBS 合并</t>
-        </is>
-      </c>
+      <c r="A1" s="6" t="n"/>
     </row>
     <row r="2" ht="20.25" customHeight="1" s="4">
       <c r="A2" s="7" t="inlineStr">

--- a/results/measurement appendix.xlsx
+++ b/results/measurement appendix.xlsx
@@ -1908,25 +1908,25 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>621.8</v>
+        <v>635.1</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>203</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.944</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.053</v>
+        <v>0.054</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.048</v>
+        <v>0.049</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>19684.1</v>
+        <v>19697.8</v>
       </c>
     </row>
     <row r="7">
@@ -1936,25 +1936,25 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>615.2</v>
+        <v>608.4</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>203</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.945</v>
+        <v>0.946</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.047</v>
+        <v>0.046</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>19679.6</v>
+        <v>19672.2</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" s="4">
@@ -1964,25 +1964,25 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>789.4</v>
+        <v>812.6</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>206</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.918</v>
+        <v>0.913</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.906</v>
+        <v>0.901</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.064</v>
+        <v>0.066</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.061</v>
+        <v>0.062</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>19847.2</v>
+        <v>19872.8</v>
       </c>
     </row>
     <row r="9">
@@ -1992,25 +1992,25 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>1158.6</v>
+        <v>1583.4</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>209</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.872</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.852</v>
+        <v>0.787</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.082</v>
+        <v>0.103</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.079</v>
+        <v>0.094</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>20206.5</v>
+        <v>20631.6</v>
       </c>
     </row>
     <row r="10" ht="33" customHeight="1" s="4">
@@ -2158,25 +2158,25 @@
         </is>
       </c>
       <c r="B6" s="17" t="n">
-        <v>45.7</v>
+        <v>62.8</v>
       </c>
       <c r="C6" s="17" t="n">
         <v>20</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>0.962</v>
+        <v>0.946</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>0.946</v>
+        <v>0.925</v>
       </c>
       <c r="F6" s="17" t="n">
-        <v>0.058</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.052</v>
+        <v>0.063</v>
       </c>
       <c r="H6" s="17" t="n">
-        <v>8964.5</v>
+        <v>9006.4</v>
       </c>
     </row>
     <row r="7" ht="59" customHeight="1" s="4">
@@ -2276,25 +2276,25 @@
         </is>
       </c>
       <c r="B4" s="10" t="n">
-        <v>24.7</v>
+        <v>22.4</v>
       </c>
       <c r="C4" s="10" t="n">
         <v>19</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>0.989</v>
+        <v>0.992</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>0.984</v>
+        <v>0.987</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>0.038</v>
+        <v>0.036</v>
       </c>
       <c r="G4" s="10" t="n">
-        <v>0.032</v>
+        <v>0.03</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>8932.1</v>
+        <v>8918.6</v>
       </c>
     </row>
     <row r="5" ht="37.5" customHeight="1" s="4">
@@ -2304,25 +2304,25 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>42.3</v>
+        <v>58.4</v>
       </c>
       <c r="C5" s="10" t="n">
         <v>20</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>0.967</v>
+        <v>0.948</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>0.953</v>
+        <v>0.929</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.056</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.049</v>
+        <v>0.061</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>8949.799999999999</v>
+        <v>8978.799999999999</v>
       </c>
     </row>
     <row r="6" ht="52" customHeight="1" s="4">
@@ -2558,22 +2558,22 @@
         <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>17.8</v>
+        <v>12.6</v>
       </c>
       <c r="D8" t="n">
         <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>0.926</v>
+        <v>0.951</v>
       </c>
       <c r="F8" t="n">
-        <v>0.852</v>
+        <v>0.902</v>
       </c>
       <c r="G8" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.063</v>
       </c>
       <c r="H8" t="n">
-        <v>0.063</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="4">
@@ -2586,22 +2586,22 @@
         <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>96.2</v>
+        <v>67.3</v>
       </c>
       <c r="D9" t="n">
         <v>35</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.962</v>
       </c>
       <c r="F9" t="n">
-        <v>0.927</v>
+        <v>0.951</v>
       </c>
       <c r="G9" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.054</v>
       </c>
       <c r="H9" t="n">
-        <v>0.058</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" s="4">
@@ -2614,22 +2614,22 @@
         <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>22.4</v>
+        <v>19.8</v>
       </c>
       <c r="D10" t="n">
         <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>0.965</v>
+        <v>0.973</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.955</v>
       </c>
       <c r="G10" t="n">
-        <v>0.064</v>
+        <v>0.054</v>
       </c>
       <c r="H10" t="n">
-        <v>0.049</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" s="4">
@@ -2642,22 +2642,22 @@
         <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>12.1</v>
+        <v>14.7</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>0.969</v>
+        <v>0.961</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.922</v>
       </c>
       <c r="G11" t="n">
-        <v>0.058</v>
+        <v>0.067</v>
       </c>
       <c r="H11" t="n">
-        <v>0.043</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="12"/>
@@ -2726,22 +2726,22 @@
         <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>21.3</v>
+        <v>17.4</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>0.972</v>
+        <v>0.978</v>
       </c>
       <c r="F16" t="n">
-        <v>0.953</v>
+        <v>0.964</v>
       </c>
       <c r="G16" t="n">
-        <v>0.057</v>
+        <v>0.049</v>
       </c>
       <c r="H16" t="n">
-        <v>0.043</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="17" ht="45" customHeight="1" s="4">
@@ -2754,22 +2754,22 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>10.7</v>
+        <v>13.9</v>
       </c>
       <c r="D17" t="n">
         <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>0.975</v>
+        <v>0.965</v>
       </c>
       <c r="F17" t="n">
-        <v>0.951</v>
+        <v>0.93</v>
       </c>
       <c r="G17" t="n">
-        <v>0.054</v>
+        <v>0.06</v>
       </c>
       <c r="H17" t="n">
-        <v>0.039</v>
+        <v>0.046</v>
       </c>
     </row>
   </sheetData>

--- a/results/measurement appendix.xlsx
+++ b/results/measurement appendix.xlsx
@@ -2418,22 +2418,22 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>24.7</v>
+        <v>26.4</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>0.971</v>
+        <v>0.968</v>
       </c>
       <c r="F3" t="n">
-        <v>0.952</v>
+        <v>0.947</v>
       </c>
       <c r="G3" t="n">
-        <v>0.058</v>
+        <v>0.075</v>
       </c>
       <c r="H3" t="n">
-        <v>0.046</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1" s="4">
@@ -2446,22 +2446,22 @@
         <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>134.3</v>
+        <v>52.7</v>
       </c>
       <c r="D4" t="n">
         <v>54</v>
       </c>
       <c r="E4" t="n">
-        <v>0.953</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9429999999999999</v>
+        <v>1.003</v>
       </c>
       <c r="G4" t="n">
-        <v>0.061</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.052</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="4">
@@ -2474,22 +2474,22 @@
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>18.6</v>
+        <v>22.4</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>0.967</v>
+        <v>0.976</v>
       </c>
       <c r="F5" t="n">
-        <v>0.945</v>
+        <v>0.96</v>
       </c>
       <c r="G5" t="n">
-        <v>0.053</v>
+        <v>0.066</v>
       </c>
       <c r="H5" t="n">
-        <v>0.041</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" s="4">
@@ -2502,22 +2502,22 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>13.4</v>
+        <v>7.5</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>0.973</v>
+        <v>0.994</v>
       </c>
       <c r="F6" t="n">
-        <v>0.946</v>
+        <v>0.989</v>
       </c>
       <c r="G6" t="n">
-        <v>0.062</v>
+        <v>0.039</v>
       </c>
       <c r="H6" t="n">
-        <v>0.045</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" s="4">
@@ -2530,22 +2530,22 @@
         <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>7.9</v>
+        <v>4.1</v>
       </c>
       <c r="D7" t="n">
         <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>0.989</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0.978</v>
+        <v>1.003</v>
       </c>
       <c r="G7" t="n">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.025</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" s="4">
@@ -2558,22 +2558,22 @@
         <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>12.6</v>
+        <v>9.1</v>
       </c>
       <c r="D8" t="n">
         <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>0.951</v>
+        <v>0.992</v>
       </c>
       <c r="F8" t="n">
-        <v>0.902</v>
+        <v>0.984</v>
       </c>
       <c r="G8" t="n">
-        <v>0.063</v>
+        <v>0.049</v>
       </c>
       <c r="H8" t="n">
-        <v>0.045</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="4">
@@ -2586,22 +2586,22 @@
         <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>67.3</v>
+        <v>82.3</v>
       </c>
       <c r="D9" t="n">
         <v>35</v>
       </c>
       <c r="E9" t="n">
-        <v>0.962</v>
+        <v>0.985</v>
       </c>
       <c r="F9" t="n">
-        <v>0.951</v>
+        <v>0.981</v>
       </c>
       <c r="G9" t="n">
-        <v>0.054</v>
+        <v>0.063</v>
       </c>
       <c r="H9" t="n">
-        <v>0.044</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" s="4">
@@ -2614,22 +2614,22 @@
         <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>19.8</v>
+        <v>18.1</v>
       </c>
       <c r="D10" t="n">
         <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>0.973</v>
+        <v>0.985</v>
       </c>
       <c r="F10" t="n">
-        <v>0.955</v>
+        <v>0.975</v>
       </c>
       <c r="G10" t="n">
-        <v>0.054</v>
+        <v>0.055</v>
       </c>
       <c r="H10" t="n">
-        <v>0.04</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" s="4">
@@ -2642,22 +2642,22 @@
         <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>14.7</v>
+        <v>6.3</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>0.961</v>
+        <v>0.997</v>
       </c>
       <c r="F11" t="n">
-        <v>0.922</v>
+        <v>0.995</v>
       </c>
       <c r="G11" t="n">
-        <v>0.067</v>
+        <v>0.028</v>
       </c>
       <c r="H11" t="n">
-        <v>0.054</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="12"/>
@@ -2726,22 +2726,22 @@
         <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>17.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>0.978</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.964</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>0.049</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.037</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="17" ht="45" customHeight="1" s="4">
@@ -2754,22 +2754,22 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>13.9</v>
+        <v>5.4</v>
       </c>
       <c r="D17" t="n">
         <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>0.965</v>
+        <v>0.999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.93</v>
+        <v>0.999</v>
       </c>
       <c r="G17" t="n">
-        <v>0.06</v>
+        <v>0.014</v>
       </c>
       <c r="H17" t="n">
-        <v>0.046</v>
+        <v>0.018</v>
       </c>
     </row>
   </sheetData>

--- a/results/measurement appendix.xlsx
+++ b/results/measurement appendix.xlsx
@@ -2418,22 +2418,22 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>26.4</v>
+        <v>41.7</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>0.968</v>
+        <v>0.926</v>
       </c>
       <c r="F3" t="n">
-        <v>0.947</v>
+        <v>0.876</v>
       </c>
       <c r="G3" t="n">
-        <v>0.075</v>
+        <v>0.103</v>
       </c>
       <c r="H3" t="n">
-        <v>0.035</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1" s="4">
@@ -2446,22 +2446,22 @@
         <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>52.7</v>
+        <v>56.7</v>
       </c>
       <c r="D4" t="n">
         <v>54</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0.994</v>
       </c>
       <c r="F4" t="n">
-        <v>1.003</v>
+        <v>0.993</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="H4" t="n">
-        <v>0.034</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="4">
@@ -2474,22 +2474,22 @@
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>22.4</v>
+        <v>51.3</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>0.976</v>
+        <v>0.902</v>
       </c>
       <c r="F5" t="n">
-        <v>0.96</v>
+        <v>0.837</v>
       </c>
       <c r="G5" t="n">
-        <v>0.066</v>
+        <v>0.118</v>
       </c>
       <c r="H5" t="n">
-        <v>0.033</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" s="4">
@@ -2502,22 +2502,22 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>7.5</v>
+        <v>25.6</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>0.994</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.989</v>
+        <v>0.886</v>
       </c>
       <c r="G6" t="n">
-        <v>0.039</v>
+        <v>0.11</v>
       </c>
       <c r="H6" t="n">
-        <v>0.021</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" s="4">
@@ -2530,22 +2530,22 @@
         <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>4.1</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
         <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0.991</v>
       </c>
       <c r="F7" t="n">
-        <v>1.003</v>
+        <v>0.982</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="H7" t="n">
-        <v>0.014</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" s="4">
@@ -2558,22 +2558,22 @@
         <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>9.1</v>
+        <v>13.7</v>
       </c>
       <c r="D8" t="n">
         <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>0.992</v>
+        <v>0.978</v>
       </c>
       <c r="F8" t="n">
-        <v>0.984</v>
+        <v>0.955</v>
       </c>
       <c r="G8" t="n">
-        <v>0.049</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>0.021</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="4">
@@ -2614,22 +2614,22 @@
         <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>18.1</v>
+        <v>31.4</v>
       </c>
       <c r="D10" t="n">
         <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>0.985</v>
+        <v>0.951</v>
       </c>
       <c r="F10" t="n">
-        <v>0.975</v>
+        <v>0.918</v>
       </c>
       <c r="G10" t="n">
-        <v>0.055</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>0.027</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" s="4">
@@ -2642,22 +2642,22 @@
         <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>6.3</v>
+        <v>11.1</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>0.997</v>
+        <v>0.983</v>
       </c>
       <c r="F11" t="n">
-        <v>0.995</v>
+        <v>0.965</v>
       </c>
       <c r="G11" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H11" t="n">
         <v>0.028</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.018</v>
       </c>
     </row>
     <row r="12"/>
@@ -2726,7 +2726,7 @@
         <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
@@ -2735,7 +2735,7 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>1.005</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -2754,19 +2754,19 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="D17" t="n">
         <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>0.999</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>0.999</v>
+        <v>1.002</v>
       </c>
       <c r="G17" t="n">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0.018</v>

--- a/results/measurement appendix.xlsx
+++ b/results/measurement appendix.xlsx
@@ -2348,7 +2348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33.375" customWidth="1" style="4" min="9" max="9"/>
@@ -2579,7 +2579,7 @@
     <row r="9" ht="15" customHeight="1" s="4">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Thriving</t>
+          <t>Thriving (T1)</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -2605,170 +2605,198 @@
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" s="4">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Self-rated OCBS</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>6</v>
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t>Thriving (T3)</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="n">
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>18.1</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="E10" t="n">
-        <v>0.985</v>
+        <v>0.964</v>
       </c>
       <c r="F10" t="n">
-        <v>0.975</v>
+        <v>0.954</v>
       </c>
       <c r="G10" t="n">
-        <v>0.055</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>0.027</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" s="4">
       <c r="A11" s="3" t="inlineStr">
         <is>
+          <t>Self-rated OCBS</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.027</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
           <t>Self-rated CWBS</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B12" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C12" t="n">
         <v>6.3</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D12" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E12" t="n">
         <v>0.997</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F12" t="n">
         <v>0.995</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G12" t="n">
         <v>0.028</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H12" t="n">
         <v>0.018</v>
       </c>
     </row>
-    <row r="12"/>
     <row r="13"/>
-    <row r="14" ht="20.25" customHeight="1" s="4">
-      <c r="A14" s="1" t="inlineStr">
+    <row r="14" ht="20.25" customHeight="1" s="4"/>
+    <row r="15" ht="28.5" customHeight="1" s="4">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>Table A2 Single-Construct CFAs for Leader-Rated Behavioral Measures</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="28.5" customHeight="1" s="4">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16" ht="45" customHeight="1" s="4">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Construct</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Items used</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>χ²</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>df</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>CFI</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>TLI</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>RMSEA</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>SRMR</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
-      </c>
-    </row>
-    <row r="16" ht="45" customHeight="1" s="4">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Leader-rated OCBS</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="C16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="D16" t="n">
-        <v>9</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.02</v>
       </c>
     </row>
     <row r="17" ht="45" customHeight="1" s="4">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>Leader-rated OCBS</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D17" t="n">
+        <v>9</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
           <t>Leader-rated CWBS</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n">
+      <c r="B18" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C18" t="n">
         <v>5.4</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D18" t="n">
         <v>5</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E18" t="n">
         <v>0.999</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F18" t="n">
         <v>0.999</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G18" t="n">
         <v>0.014</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H18" t="n">
         <v>0.018</v>
       </c>
     </row>

--- a/results/measurement appendix.xlsx
+++ b/results/measurement appendix.xlsx
@@ -2348,7 +2348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33.375" customWidth="1" style="4" min="9" max="9"/>
@@ -2579,7 +2579,7 @@
     <row r="9" ht="15" customHeight="1" s="4">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Thriving</t>
+          <t>Thriving (T1)</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -2605,170 +2605,198 @@
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" s="4">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Self-rated OCBS</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>6</v>
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t>Thriving (T3)</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="n">
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>31.4</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="E10" t="n">
-        <v>0.951</v>
+        <v>0.964</v>
       </c>
       <c r="F10" t="n">
-        <v>0.918</v>
+        <v>0.954</v>
       </c>
       <c r="G10" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>0.04</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" s="4">
       <c r="A11" s="3" t="inlineStr">
         <is>
+          <t>Self-rated OCBS</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.951</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
           <t>Self-rated CWBS</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B12" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C12" t="n">
         <v>11.1</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D12" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E12" t="n">
         <v>0.983</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F12" t="n">
         <v>0.965</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G12" t="n">
         <v>0.06</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H12" t="n">
         <v>0.028</v>
       </c>
     </row>
-    <row r="12"/>
     <row r="13"/>
-    <row r="14" ht="20.25" customHeight="1" s="4">
-      <c r="A14" s="1" t="inlineStr">
+    <row r="14" ht="20.25" customHeight="1" s="4"/>
+    <row r="15" ht="28.5" customHeight="1" s="4">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>Table A2 Single-Construct CFAs for Leader-Rated Behavioral Measures</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="28.5" customHeight="1" s="4">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16" ht="45" customHeight="1" s="4">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Construct</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Items used</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>χ²</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>df</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>CFI</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>TLI</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>RMSEA</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>SRMR</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
-      </c>
-    </row>
-    <row r="16" ht="45" customHeight="1" s="4">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Leader-rated OCBS</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="C16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="D16" t="n">
-        <v>9</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1.005</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.02</v>
       </c>
     </row>
     <row r="17" ht="45" customHeight="1" s="4">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Leader-rated CWBS</t>
+          <t>Leader-rated OCBS</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>4.7</v>
+        <v>7.6</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>1.002</v>
+        <v>1.005</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Leader-rated CWBS</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.002</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
         <v>0.018</v>
       </c>
     </row>

--- a/results/measurement appendix.xlsx
+++ b/results/measurement appendix.xlsx
@@ -2418,22 +2418,22 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>26.4</v>
+        <v>33.5</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>0.968</v>
+        <v>0.956</v>
       </c>
       <c r="F3" t="n">
-        <v>0.947</v>
+        <v>0.927</v>
       </c>
       <c r="G3" t="n">
-        <v>0.075</v>
+        <v>0.089</v>
       </c>
       <c r="H3" t="n">
-        <v>0.035</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1" s="4">
@@ -2446,22 +2446,22 @@
         <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>52.7</v>
+        <v>86.2</v>
       </c>
       <c r="D4" t="n">
         <v>54</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0.953</v>
       </c>
       <c r="F4" t="n">
-        <v>1.003</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="H4" t="n">
-        <v>0.034</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="4">
@@ -2474,22 +2474,22 @@
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>22.4</v>
+        <v>25.2</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>0.976</v>
+        <v>0.972</v>
       </c>
       <c r="F5" t="n">
-        <v>0.96</v>
+        <v>0.953</v>
       </c>
       <c r="G5" t="n">
-        <v>0.066</v>
+        <v>0.073</v>
       </c>
       <c r="H5" t="n">
-        <v>0.033</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" s="4">
@@ -2502,22 +2502,22 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>7.5</v>
+        <v>20.7</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>0.994</v>
+        <v>0.966</v>
       </c>
       <c r="F6" t="n">
-        <v>0.989</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>0.039</v>
+        <v>0.096</v>
       </c>
       <c r="H6" t="n">
-        <v>0.021</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" s="4">
@@ -2530,22 +2530,22 @@
         <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>4.1</v>
+        <v>38.8</v>
       </c>
       <c r="D7" t="n">
         <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>1.003</v>
+        <v>0.882</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>0.141</v>
       </c>
       <c r="H7" t="n">
-        <v>0.014</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" s="4">
@@ -2558,22 +2558,22 @@
         <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>9.1</v>
+        <v>35</v>
       </c>
       <c r="D8" t="n">
         <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>0.992</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>0.984</v>
+        <v>0.886</v>
       </c>
       <c r="G8" t="n">
-        <v>0.049</v>
+        <v>0.133</v>
       </c>
       <c r="H8" t="n">
-        <v>0.021</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="4">
@@ -2586,22 +2586,22 @@
         <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>82.3</v>
+        <v>111</v>
       </c>
       <c r="D9" t="n">
         <v>35</v>
       </c>
       <c r="E9" t="n">
-        <v>0.985</v>
+        <v>0.964</v>
       </c>
       <c r="F9" t="n">
-        <v>0.981</v>
+        <v>0.953</v>
       </c>
       <c r="G9" t="n">
-        <v>0.063</v>
+        <v>0.08</v>
       </c>
       <c r="H9" t="n">
-        <v>0.019</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" s="4">
@@ -2614,22 +2614,22 @@
         <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>97.09999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="D10" t="n">
         <v>35</v>
       </c>
       <c r="E10" t="n">
-        <v>0.964</v>
+        <v>0.984</v>
       </c>
       <c r="F10" t="n">
-        <v>0.954</v>
+        <v>0.98</v>
       </c>
       <c r="G10" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.054</v>
       </c>
       <c r="H10" t="n">
-        <v>0.036</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" s="4">
@@ -2642,22 +2642,22 @@
         <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>18.1</v>
+        <v>37.7</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>0.985</v>
+        <v>0.95</v>
       </c>
       <c r="F11" t="n">
-        <v>0.975</v>
+        <v>0.916</v>
       </c>
       <c r="G11" t="n">
-        <v>0.055</v>
+        <v>0.097</v>
       </c>
       <c r="H11" t="n">
-        <v>0.027</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="12">
@@ -2670,22 +2670,22 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>6.3</v>
+        <v>31.4</v>
       </c>
       <c r="D12" t="n">
         <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>0.997</v>
+        <v>0.944</v>
       </c>
       <c r="F12" t="n">
-        <v>0.995</v>
+        <v>0.888</v>
       </c>
       <c r="G12" t="n">
-        <v>0.028</v>
+        <v>0.125</v>
       </c>
       <c r="H12" t="n">
-        <v>0.018</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="13"/>
@@ -2754,22 +2754,22 @@
         <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>8.800000000000001</v>
+        <v>40.3</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0.947</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0.911</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.101</v>
       </c>
       <c r="H17" t="n">
-        <v>0.02</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="18">
@@ -2782,22 +2782,22 @@
         <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>5.4</v>
+        <v>31.6</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>0.999</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>0.999</v>
+        <v>0.886</v>
       </c>
       <c r="G18" t="n">
-        <v>0.014</v>
+        <v>0.125</v>
       </c>
       <c r="H18" t="n">
-        <v>0.018</v>
+        <v>0.043</v>
       </c>
     </row>
   </sheetData>

--- a/results/measurement appendix.xlsx
+++ b/results/measurement appendix.xlsx
@@ -2418,22 +2418,22 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>41.7</v>
+        <v>30.4</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>0.926</v>
+        <v>0.949</v>
       </c>
       <c r="F3" t="n">
-        <v>0.876</v>
+        <v>0.916</v>
       </c>
       <c r="G3" t="n">
-        <v>0.103</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>0.049</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1" s="4">
@@ -2446,22 +2446,22 @@
         <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>56.7</v>
+        <v>95.7</v>
       </c>
       <c r="D4" t="n">
         <v>54</v>
       </c>
       <c r="E4" t="n">
-        <v>0.994</v>
+        <v>0.918</v>
       </c>
       <c r="F4" t="n">
-        <v>0.993</v>
+        <v>0.899</v>
       </c>
       <c r="G4" t="n">
-        <v>0.012</v>
+        <v>0.048</v>
       </c>
       <c r="H4" t="n">
-        <v>0.036</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="4">
@@ -2474,7 +2474,7 @@
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>51.3</v>
+        <v>50.9</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
@@ -2486,10 +2486,10 @@
         <v>0.837</v>
       </c>
       <c r="G5" t="n">
-        <v>0.118</v>
+        <v>0.117</v>
       </c>
       <c r="H5" t="n">
-        <v>0.056</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" s="4">
@@ -2502,22 +2502,22 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>25.6</v>
+        <v>38.6</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.907</v>
       </c>
       <c r="F6" t="n">
-        <v>0.886</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>0.11</v>
+        <v>0.141</v>
       </c>
       <c r="H6" t="n">
-        <v>0.042</v>
+        <v>0.059</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" s="4">
@@ -2530,22 +2530,22 @@
         <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>55.9</v>
       </c>
       <c r="D7" t="n">
         <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>0.991</v>
+        <v>0.895</v>
       </c>
       <c r="F7" t="n">
-        <v>0.982</v>
+        <v>0.789</v>
       </c>
       <c r="G7" t="n">
-        <v>0.048</v>
+        <v>0.173</v>
       </c>
       <c r="H7" t="n">
-        <v>0.022</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" s="4">
@@ -2558,22 +2558,22 @@
         <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>13.7</v>
+        <v>45.4</v>
       </c>
       <c r="D8" t="n">
         <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>0.978</v>
+        <v>0.903</v>
       </c>
       <c r="F8" t="n">
-        <v>0.955</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.154</v>
       </c>
       <c r="H8" t="n">
-        <v>0.029</v>
+        <v>0.062</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="4">
@@ -2586,22 +2586,22 @@
         <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>82.3</v>
+        <v>247.9</v>
       </c>
       <c r="D9" t="n">
         <v>35</v>
       </c>
       <c r="E9" t="n">
-        <v>0.985</v>
+        <v>0.878</v>
       </c>
       <c r="F9" t="n">
-        <v>0.981</v>
+        <v>0.843</v>
       </c>
       <c r="G9" t="n">
-        <v>0.063</v>
+        <v>0.134</v>
       </c>
       <c r="H9" t="n">
-        <v>0.019</v>
+        <v>0.097</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" s="4">
@@ -2614,22 +2614,22 @@
         <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>97.09999999999999</v>
+        <v>294.2</v>
       </c>
       <c r="D10" t="n">
         <v>35</v>
       </c>
       <c r="E10" t="n">
-        <v>0.964</v>
+        <v>0.827</v>
       </c>
       <c r="F10" t="n">
-        <v>0.954</v>
+        <v>0.778</v>
       </c>
       <c r="G10" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.148</v>
       </c>
       <c r="H10" t="n">
-        <v>0.036</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" s="4">
@@ -2642,22 +2642,22 @@
         <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>31.4</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>0.951</v>
+        <v>0.868</v>
       </c>
       <c r="F11" t="n">
-        <v>0.918</v>
+        <v>0.781</v>
       </c>
       <c r="G11" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.143</v>
       </c>
       <c r="H11" t="n">
-        <v>0.04</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="12">
@@ -2670,22 +2670,22 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>11.1</v>
+        <v>47.4</v>
       </c>
       <c r="D12" t="n">
         <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>0.983</v>
+        <v>0.89</v>
       </c>
       <c r="F12" t="n">
-        <v>0.965</v>
+        <v>0.781</v>
       </c>
       <c r="G12" t="n">
-        <v>0.06</v>
+        <v>0.158</v>
       </c>
       <c r="H12" t="n">
-        <v>0.028</v>
+        <v>0.06900000000000001</v>
       </c>
     </row>
     <row r="13"/>
@@ -2754,22 +2754,22 @@
         <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>7.6</v>
+        <v>61.8</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0.892</v>
       </c>
       <c r="F17" t="n">
-        <v>1.005</v>
+        <v>0.82</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.131</v>
       </c>
       <c r="H17" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="18">
@@ -2782,22 +2782,22 @@
         <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>4.7</v>
+        <v>37.9</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0.913</v>
       </c>
       <c r="F18" t="n">
-        <v>1.002</v>
+        <v>0.825</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.139</v>
       </c>
       <c r="H18" t="n">
-        <v>0.018</v>
+        <v>0.051</v>
       </c>
     </row>
   </sheetData>
